--- a/public/informes-templates/INFORME DE PC.xlsx
+++ b/public/informes-templates/INFORME DE PC.xlsx
@@ -1,53 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SIP-APP\SIPAPP-HUAQUIAN\Frontend\public\informes-templates\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81F8A34-34E8-4E23-B232-17B8E811AA3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1737323A-14A1-4D31-B526-62B41CFB2DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Gi6r7bJTU3p7kLKVhXqMBCIqgtZftuSTomlqvp8mivE="/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>INFORME DE SERVICIO</t>
   </si>
@@ -70,13 +38,7 @@
     <t xml:space="preserve">DESCRIPCION </t>
   </si>
   <si>
-    <t>SERVICIO DE MANTENIMIENTO</t>
-  </si>
-  <si>
     <t>TIPO</t>
-  </si>
-  <si>
-    <t>VARIADORES</t>
   </si>
   <si>
     <t>CANTIDAD</t>
@@ -113,9 +75,6 @@
   </si>
   <si>
     <t xml:space="preserve">OBSERVACION </t>
-  </si>
-  <si>
-    <t>El equipo ingreso contaminado.</t>
   </si>
   <si>
     <t>FOTOS DEL EQUIPO</t>
@@ -190,30 +149,19 @@
     <t>CONCLUSIONES</t>
   </si>
   <si>
-    <t>Se realizó la limpieza interna del equipo, eliminando la contaminación presente en la tarjeta de potencia y en la carcasa, restableciendo condiciones adecuadas de operación.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se efectuo del cambio de </t>
-  </si>
-  <si>
     <t>RECOMENDACIONES</t>
-  </si>
-  <si>
-    <t>Implementar un programa de mantenimiento preventivo de 12 meses.</t>
-  </si>
-  <si>
-    <t>Mejorar la ambientacion del equipo, para evitar una mayor contaminacion y prolongar su tiempo de uso.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -271,6 +219,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <i/>
@@ -482,10 +436,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+  <cellXfs count="43">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -504,8 +456,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -513,17 +465,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -531,11 +483,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -549,44 +507,62 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -605,68 +581,53 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -871,13 +832,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z169"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="9" width="17.83203125" customWidth="1"/>
+    <col min="1" max="9" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="8"/>
@@ -906,16 +867,16 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="17"/>
+    <row r="2" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="12"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -934,15 +895,13 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="25" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+    <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13"/>
       <c r="B3" s="9"/>
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="7"/>
+      <c r="D3" s="16"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
@@ -966,13 +925,13 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14"/>
       <c r="B4" s="15"/>
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="7"/>
+      <c r="D4" s="16"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
@@ -996,13 +955,13 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14"/>
       <c r="B5" s="15"/>
       <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="7"/>
+      <c r="D5" s="16"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
@@ -1026,13 +985,13 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14"/>
       <c r="B6" s="15"/>
       <c r="C6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="7"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -1056,13 +1015,13 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15"/>
       <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="7"/>
+      <c r="D7" s="16"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
@@ -1086,15 +1045,13 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="15"/>
       <c r="C8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="D8" s="17"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -1118,15 +1075,13 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="15"/>
       <c r="C9" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>9</v>
-      </c>
+      <c r="D9" s="17"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -1150,13 +1105,13 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14"/>
       <c r="B10" s="15"/>
       <c r="C10" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
-      <c r="D10" s="7"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -1180,13 +1135,13 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="15"/>
       <c r="C11" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
-      <c r="D11" s="7"/>
+      <c r="D11" s="16"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
@@ -1210,16 +1165,16 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
+    <row r="12" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="18"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -1238,20 +1193,20 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="13" t="s">
-        <v>12</v>
+    <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
+        <v>10</v>
       </c>
       <c r="B13" s="9"/>
-      <c r="C13" s="18" t="s">
-        <v>13</v>
+      <c r="C13" s="20" t="s">
+        <v>11</v>
       </c>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="20"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="22"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -1270,27 +1225,27 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14"/>
       <c r="B14" s="15"/>
       <c r="C14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="F14" s="22"/>
+      <c r="G14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="H14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="20"/>
-      <c r="G14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1310,13 +1265,13 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14"/>
       <c r="B15" s="15"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="20"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="22"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -1338,18 +1293,16 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14"/>
       <c r="B16" s="15"/>
       <c r="C16" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
-      <c r="D16" s="22" t="s">
-        <v>21</v>
+      <c r="D16" s="25" t="s">
+        <v>19</v>
       </c>
-      <c r="E16" s="24" t="s">
-        <v>22</v>
-      </c>
+      <c r="E16" s="24"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
@@ -1372,16 +1325,16 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
+    <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10"/>
+      <c r="B17" s="12"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="17"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="12"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -1400,18 +1353,18 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="33" t="s">
-        <v>23</v>
+    <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27" t="s">
+        <v>20</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="20"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="22"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -1430,16 +1383,16 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="25"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="9"/>
+    <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="34"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="36"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -1458,16 +1411,16 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="14"/>
-      <c r="B20" s="26"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="15"/>
+    <row r="20" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="37"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="39"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -1486,16 +1439,16 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="14"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="15"/>
+    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="37"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="39"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -1514,16 +1467,16 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="14"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="15"/>
+    <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="37"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="39"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -1542,16 +1495,16 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="14"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="15"/>
+    <row r="23" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="37"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="39"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -1570,16 +1523,16 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="14"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="15"/>
+    <row r="24" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="37"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="39"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -1598,16 +1551,16 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="14"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="15"/>
+    <row r="25" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="37"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="39"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -1626,16 +1579,16 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="14"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="15"/>
+    <row r="26" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="37"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="39"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -1654,16 +1607,16 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="14"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="15"/>
+    <row r="27" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="37"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="39"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -1682,16 +1635,16 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="14"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="15"/>
+    <row r="28" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="37"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="39"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -1710,16 +1663,16 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="14"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="15"/>
+    <row r="29" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="37"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="39"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -1738,16 +1691,16 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="14"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="15"/>
+    <row r="30" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="37"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="39"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -1766,16 +1719,16 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="14"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="15"/>
+    <row r="31" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="37"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="39"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -1794,16 +1747,16 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="14"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="15"/>
+    <row r="32" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="37"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="39"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -1822,16 +1775,16 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="14"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="15"/>
+    <row r="33" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="37"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="39"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -1850,16 +1803,16 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="14"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="15"/>
+    <row r="34" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="37"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="39"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -1878,16 +1831,16 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="14"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="15"/>
+    <row r="35" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="37"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="39"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -1906,16 +1859,16 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="14"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="15"/>
+    <row r="36" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="37"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="39"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -1934,16 +1887,16 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="14"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="15"/>
+    <row r="37" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="37"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="39"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -1962,16 +1915,16 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="14"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="17"/>
+    <row r="38" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="37"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="41"/>
+      <c r="I38" s="42"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -1990,22 +1943,22 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A39" s="27" t="s">
-        <v>24</v>
+    <row r="39" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="28" t="s">
+        <v>21</v>
       </c>
-      <c r="B39" s="19"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="27" t="s">
-        <v>25</v>
+      <c r="B39" s="21"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="28" t="s">
+        <v>22</v>
       </c>
-      <c r="E39" s="19"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="27" t="s">
-        <v>26</v>
+      <c r="E39" s="21"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="28" t="s">
+        <v>23</v>
       </c>
-      <c r="H39" s="19"/>
-      <c r="I39" s="20"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="22"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -2024,16 +1977,16 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A40" s="25"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="9"/>
+    <row r="40" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="34"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="36"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -2052,16 +2005,16 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A41" s="14"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="15"/>
+    <row r="41" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="37"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="39"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -2080,16 +2033,16 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A42" s="14"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="15"/>
+    <row r="42" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="37"/>
+      <c r="B42" s="38"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="38"/>
+      <c r="I42" s="39"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -2108,16 +2061,16 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A43" s="14"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="15"/>
+    <row r="43" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="37"/>
+      <c r="B43" s="38"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="39"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="39"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -2136,16 +2089,16 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A44" s="14"/>
-      <c r="B44" s="26"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="26"/>
-      <c r="I44" s="15"/>
+    <row r="44" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="37"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="39"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="39"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
@@ -2164,16 +2117,16 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A45" s="14"/>
-      <c r="B45" s="26"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="15"/>
+    <row r="45" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="37"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="39"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="39"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
@@ -2192,16 +2145,16 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A46" s="14"/>
-      <c r="B46" s="26"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="15"/>
+    <row r="46" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="37"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="39"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="39"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="39"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
@@ -2220,16 +2173,16 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A47" s="14"/>
-      <c r="B47" s="26"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="15"/>
+    <row r="47" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="37"/>
+      <c r="B47" s="38"/>
+      <c r="C47" s="39"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="39"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="38"/>
+      <c r="I47" s="39"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -2248,16 +2201,16 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A48" s="14"/>
-      <c r="B48" s="26"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="26"/>
-      <c r="I48" s="15"/>
+    <row r="48" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="37"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="39"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="38"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="37"/>
+      <c r="H48" s="38"/>
+      <c r="I48" s="39"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -2276,16 +2229,16 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A49" s="14"/>
-      <c r="B49" s="26"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="17"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="15"/>
+    <row r="49" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="37"/>
+      <c r="B49" s="38"/>
+      <c r="C49" s="39"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="37"/>
+      <c r="H49" s="38"/>
+      <c r="I49" s="39"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -2304,16 +2257,16 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A50" s="14"/>
-      <c r="B50" s="26"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="25"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="26"/>
-      <c r="I50" s="15"/>
+    <row r="50" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="37"/>
+      <c r="B50" s="38"/>
+      <c r="C50" s="39"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="35"/>
+      <c r="F50" s="36"/>
+      <c r="G50" s="37"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="39"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -2332,16 +2285,16 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A51" s="14"/>
-      <c r="B51" s="26"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="26"/>
-      <c r="I51" s="15"/>
+    <row r="51" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="37"/>
+      <c r="B51" s="38"/>
+      <c r="C51" s="39"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="38"/>
+      <c r="F51" s="39"/>
+      <c r="G51" s="37"/>
+      <c r="H51" s="38"/>
+      <c r="I51" s="39"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -2360,16 +2313,16 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A52" s="14"/>
-      <c r="B52" s="26"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="26"/>
-      <c r="I52" s="15"/>
+    <row r="52" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="37"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="39"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="38"/>
+      <c r="F52" s="39"/>
+      <c r="G52" s="37"/>
+      <c r="H52" s="38"/>
+      <c r="I52" s="39"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -2388,16 +2341,16 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A53" s="14"/>
-      <c r="B53" s="26"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="26"/>
-      <c r="I53" s="15"/>
+    <row r="53" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="37"/>
+      <c r="B53" s="38"/>
+      <c r="C53" s="39"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="39"/>
+      <c r="G53" s="37"/>
+      <c r="H53" s="38"/>
+      <c r="I53" s="39"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -2416,16 +2369,16 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A54" s="14"/>
-      <c r="B54" s="26"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="15"/>
+    <row r="54" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="37"/>
+      <c r="B54" s="38"/>
+      <c r="C54" s="39"/>
+      <c r="D54" s="37"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="39"/>
+      <c r="G54" s="37"/>
+      <c r="H54" s="38"/>
+      <c r="I54" s="39"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -2444,16 +2397,16 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A55" s="14"/>
-      <c r="B55" s="26"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="26"/>
-      <c r="I55" s="15"/>
+    <row r="55" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="37"/>
+      <c r="B55" s="38"/>
+      <c r="C55" s="39"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="38"/>
+      <c r="F55" s="39"/>
+      <c r="G55" s="37"/>
+      <c r="H55" s="38"/>
+      <c r="I55" s="39"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -2472,16 +2425,16 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A56" s="14"/>
-      <c r="B56" s="26"/>
-      <c r="C56" s="15"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="26"/>
-      <c r="I56" s="15"/>
+    <row r="56" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="37"/>
+      <c r="B56" s="38"/>
+      <c r="C56" s="39"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="38"/>
+      <c r="F56" s="39"/>
+      <c r="G56" s="37"/>
+      <c r="H56" s="38"/>
+      <c r="I56" s="39"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
@@ -2500,16 +2453,16 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A57" s="14"/>
-      <c r="B57" s="26"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="26"/>
-      <c r="I57" s="15"/>
+    <row r="57" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="37"/>
+      <c r="B57" s="38"/>
+      <c r="C57" s="39"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="38"/>
+      <c r="F57" s="39"/>
+      <c r="G57" s="37"/>
+      <c r="H57" s="38"/>
+      <c r="I57" s="39"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
@@ -2528,16 +2481,16 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A58" s="14"/>
-      <c r="B58" s="26"/>
-      <c r="C58" s="15"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="26"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="26"/>
-      <c r="I58" s="15"/>
+    <row r="58" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="37"/>
+      <c r="B58" s="38"/>
+      <c r="C58" s="39"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="38"/>
+      <c r="F58" s="39"/>
+      <c r="G58" s="37"/>
+      <c r="H58" s="38"/>
+      <c r="I58" s="39"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
@@ -2556,16 +2509,16 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A59" s="14"/>
-      <c r="B59" s="26"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="17"/>
-      <c r="G59" s="16"/>
-      <c r="H59" s="12"/>
-      <c r="I59" s="17"/>
+    <row r="59" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="37"/>
+      <c r="B59" s="38"/>
+      <c r="C59" s="39"/>
+      <c r="D59" s="40"/>
+      <c r="E59" s="41"/>
+      <c r="F59" s="42"/>
+      <c r="G59" s="40"/>
+      <c r="H59" s="41"/>
+      <c r="I59" s="42"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -2584,22 +2537,22 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A60" s="27" t="s">
-        <v>27</v>
+    <row r="60" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="28" t="s">
+        <v>24</v>
       </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="27" t="s">
-        <v>28</v>
+      <c r="B60" s="21"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="28" t="s">
+        <v>25</v>
       </c>
-      <c r="E60" s="19"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="27" t="s">
-        <v>29</v>
+      <c r="E60" s="21"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="28" t="s">
+        <v>26</v>
       </c>
-      <c r="H60" s="19"/>
-      <c r="I60" s="20"/>
+      <c r="H60" s="21"/>
+      <c r="I60" s="22"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
@@ -2618,7 +2571,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -2646,18 +2599,18 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A62" s="27" t="s">
-        <v>30</v>
+    <row r="62" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="28" t="s">
+        <v>27</v>
       </c>
-      <c r="B62" s="19"/>
-      <c r="C62" s="19"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="19"/>
-      <c r="F62" s="19"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="19"/>
-      <c r="I62" s="20"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="21"/>
+      <c r="G62" s="21"/>
+      <c r="H62" s="21"/>
+      <c r="I62" s="22"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
@@ -2676,20 +2629,20 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
-      <c r="B63" s="18" t="s">
-        <v>31</v>
+      <c r="B63" s="20" t="s">
+        <v>28</v>
       </c>
-      <c r="C63" s="19"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="19"/>
-      <c r="F63" s="19"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="19"/>
-      <c r="I63" s="20"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="21"/>
+      <c r="H63" s="21"/>
+      <c r="I63" s="22"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
@@ -2708,16 +2661,16 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
-      <c r="B64" s="21"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="20"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
+      <c r="H64" s="21"/>
+      <c r="I64" s="22"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -2736,16 +2689,16 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4"/>
-      <c r="B65" s="21"/>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="20"/>
+      <c r="B65" s="23"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="21"/>
+      <c r="G65" s="21"/>
+      <c r="H65" s="21"/>
+      <c r="I65" s="22"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
@@ -2764,16 +2717,16 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4"/>
-      <c r="B66" s="21"/>
-      <c r="C66" s="19"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="19"/>
-      <c r="F66" s="19"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="19"/>
-      <c r="I66" s="20"/>
+      <c r="B66" s="23"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="21"/>
+      <c r="G66" s="21"/>
+      <c r="H66" s="21"/>
+      <c r="I66" s="22"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
@@ -2792,16 +2745,16 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4"/>
-      <c r="B67" s="21"/>
-      <c r="C67" s="19"/>
-      <c r="D67" s="19"/>
-      <c r="E67" s="19"/>
-      <c r="F67" s="19"/>
-      <c r="G67" s="19"/>
-      <c r="H67" s="19"/>
-      <c r="I67" s="20"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="21"/>
+      <c r="H67" s="21"/>
+      <c r="I67" s="22"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
@@ -2820,9 +2773,9 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A68" s="34" t="s">
-        <v>32</v>
+    <row r="68" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="29" t="s">
+        <v>29</v>
       </c>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -2850,23 +2803,23 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
-      <c r="B69" s="18" t="s">
-        <v>34</v>
+      <c r="B69" s="20" t="s">
+        <v>31</v>
       </c>
-      <c r="C69" s="19"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="19"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
       <c r="H69" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -2886,18 +2839,18 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>1</v>
       </c>
-      <c r="B70" s="28" t="s">
-        <v>37</v>
+      <c r="B70" s="30" t="s">
+        <v>34</v>
       </c>
-      <c r="C70" s="19"/>
-      <c r="D70" s="19"/>
-      <c r="E70" s="19"/>
-      <c r="F70" s="19"/>
-      <c r="G70" s="20"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="22"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
       <c r="J70" s="1"/>
@@ -2918,18 +2871,18 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>2</v>
       </c>
-      <c r="B71" s="28" t="s">
-        <v>38</v>
+      <c r="B71" s="30" t="s">
+        <v>35</v>
       </c>
-      <c r="C71" s="19"/>
-      <c r="D71" s="19"/>
-      <c r="E71" s="19"/>
-      <c r="F71" s="19"/>
-      <c r="G71" s="20"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="22"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
       <c r="J71" s="1"/>
@@ -2950,18 +2903,18 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>3</v>
       </c>
-      <c r="B72" s="28" t="s">
-        <v>39</v>
+      <c r="B72" s="30" t="s">
+        <v>36</v>
       </c>
-      <c r="C72" s="19"/>
-      <c r="D72" s="19"/>
-      <c r="E72" s="19"/>
-      <c r="F72" s="19"/>
-      <c r="G72" s="20"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="22"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
       <c r="J72" s="1"/>
@@ -2982,18 +2935,18 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>4</v>
       </c>
-      <c r="B73" s="28" t="s">
-        <v>40</v>
+      <c r="B73" s="30" t="s">
+        <v>37</v>
       </c>
-      <c r="C73" s="19"/>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="20"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="22"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
       <c r="J73" s="1"/>
@@ -3014,18 +2967,18 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>5</v>
       </c>
-      <c r="B74" s="28" t="s">
-        <v>41</v>
+      <c r="B74" s="30" t="s">
+        <v>38</v>
       </c>
-      <c r="C74" s="19"/>
-      <c r="D74" s="19"/>
-      <c r="E74" s="19"/>
-      <c r="F74" s="19"/>
-      <c r="G74" s="20"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="22"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
       <c r="J74" s="1"/>
@@ -3046,18 +2999,18 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>6</v>
       </c>
-      <c r="B75" s="28" t="s">
-        <v>42</v>
+      <c r="B75" s="30" t="s">
+        <v>39</v>
       </c>
-      <c r="C75" s="19"/>
-      <c r="D75" s="19"/>
-      <c r="E75" s="19"/>
-      <c r="F75" s="19"/>
-      <c r="G75" s="20"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="21"/>
+      <c r="G75" s="22"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
       <c r="J75" s="1"/>
@@ -3078,18 +3031,18 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>7</v>
       </c>
-      <c r="B76" s="28" t="s">
-        <v>43</v>
+      <c r="B76" s="30" t="s">
+        <v>40</v>
       </c>
-      <c r="C76" s="19"/>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="19"/>
-      <c r="G76" s="20"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="21"/>
+      <c r="F76" s="21"/>
+      <c r="G76" s="22"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
       <c r="J76" s="1"/>
@@ -3110,18 +3063,18 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>8</v>
       </c>
-      <c r="B77" s="28" t="s">
-        <v>44</v>
+      <c r="B77" s="30" t="s">
+        <v>41</v>
       </c>
-      <c r="C77" s="19"/>
-      <c r="D77" s="19"/>
-      <c r="E77" s="19"/>
-      <c r="F77" s="19"/>
-      <c r="G77" s="20"/>
+      <c r="C77" s="21"/>
+      <c r="D77" s="21"/>
+      <c r="E77" s="21"/>
+      <c r="F77" s="21"/>
+      <c r="G77" s="22"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
       <c r="J77" s="1"/>
@@ -3142,18 +3095,18 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>9</v>
       </c>
-      <c r="B78" s="28" t="s">
-        <v>45</v>
+      <c r="B78" s="30" t="s">
+        <v>42</v>
       </c>
-      <c r="C78" s="19"/>
-      <c r="D78" s="19"/>
-      <c r="E78" s="19"/>
-      <c r="F78" s="19"/>
-      <c r="G78" s="20"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="21"/>
+      <c r="F78" s="21"/>
+      <c r="G78" s="22"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
       <c r="J78" s="1"/>
@@ -3174,9 +3127,9 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="29" t="s">
-        <v>46</v>
+    <row r="79" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="31" t="s">
+        <v>43</v>
       </c>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
@@ -3204,10 +3157,8 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="30" t="s">
-        <v>47</v>
-      </c>
+    <row r="80" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="32"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
@@ -3234,10 +3185,8 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A81" s="30" t="s">
-        <v>48</v>
-      </c>
+    <row r="81" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="32"/>
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
@@ -3264,9 +3213,9 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A82" s="29" t="s">
-        <v>49</v>
+    <row r="82" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="31" t="s">
+        <v>44</v>
       </c>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
@@ -3294,18 +3243,16 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A83" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B83" s="19"/>
-      <c r="C83" s="19"/>
-      <c r="D83" s="19"/>
-      <c r="E83" s="19"/>
-      <c r="F83" s="19"/>
-      <c r="G83" s="19"/>
-      <c r="H83" s="19"/>
-      <c r="I83" s="20"/>
+    <row r="83" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="33"/>
+      <c r="B83" s="21"/>
+      <c r="C83" s="21"/>
+      <c r="D83" s="21"/>
+      <c r="E83" s="21"/>
+      <c r="F83" s="21"/>
+      <c r="G83" s="21"/>
+      <c r="H83" s="21"/>
+      <c r="I83" s="22"/>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
@@ -3324,18 +3271,16 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="B84" s="19"/>
-      <c r="C84" s="19"/>
-      <c r="D84" s="19"/>
-      <c r="E84" s="19"/>
-      <c r="F84" s="19"/>
-      <c r="G84" s="19"/>
-      <c r="H84" s="19"/>
-      <c r="I84" s="20"/>
+    <row r="84" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="33"/>
+      <c r="B84" s="21"/>
+      <c r="C84" s="21"/>
+      <c r="D84" s="21"/>
+      <c r="E84" s="21"/>
+      <c r="F84" s="21"/>
+      <c r="G84" s="21"/>
+      <c r="H84" s="21"/>
+      <c r="I84" s="22"/>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
@@ -3354,7 +3299,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3382,7 +3327,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3410,7 +3355,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3438,7 +3383,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3466,7 +3411,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3494,7 +3439,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3522,7 +3467,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3550,7 +3495,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3578,7 +3523,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3606,7 +3551,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3634,7 +3579,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3662,7 +3607,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3690,7 +3635,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3718,7 +3663,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3746,7 +3691,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3774,7 +3719,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3802,7 +3747,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3830,7 +3775,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3858,7 +3803,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3886,7 +3831,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3914,7 +3859,7 @@
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
     </row>
-    <row r="105" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3942,7 +3887,7 @@
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
     </row>
-    <row r="106" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3970,7 +3915,7 @@
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
     </row>
-    <row r="107" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3998,7 +3943,7 @@
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
     </row>
-    <row r="108" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -4026,7 +3971,7 @@
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
     </row>
-    <row r="109" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4054,7 +3999,7 @@
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
     </row>
-    <row r="110" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4082,7 +4027,7 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
     </row>
-    <row r="111" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4110,7 +4055,7 @@
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
     </row>
-    <row r="112" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4138,7 +4083,7 @@
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
     </row>
-    <row r="113" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4166,7 +4111,7 @@
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
     </row>
-    <row r="114" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4194,7 +4139,7 @@
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
     </row>
-    <row r="115" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4222,7 +4167,7 @@
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
     </row>
-    <row r="116" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4250,7 +4195,7 @@
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
     </row>
-    <row r="117" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4278,7 +4223,7 @@
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
     </row>
-    <row r="118" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4306,7 +4251,7 @@
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
     </row>
-    <row r="119" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4334,7 +4279,7 @@
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
     </row>
-    <row r="120" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4362,7 +4307,7 @@
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
     </row>
-    <row r="121" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4390,7 +4335,7 @@
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
     </row>
-    <row r="122" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4418,7 +4363,7 @@
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
     </row>
-    <row r="123" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4446,7 +4391,7 @@
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
     </row>
-    <row r="124" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4474,7 +4419,7 @@
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
     </row>
-    <row r="125" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4502,7 +4447,7 @@
       <c r="Y125" s="1"/>
       <c r="Z125" s="1"/>
     </row>
-    <row r="126" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4530,7 +4475,7 @@
       <c r="Y126" s="1"/>
       <c r="Z126" s="1"/>
     </row>
-    <row r="127" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4558,7 +4503,7 @@
       <c r="Y127" s="1"/>
       <c r="Z127" s="1"/>
     </row>
-    <row r="128" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4586,7 +4531,7 @@
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
     </row>
-    <row r="129" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4614,7 +4559,7 @@
       <c r="Y129" s="1"/>
       <c r="Z129" s="1"/>
     </row>
-    <row r="130" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4642,7 +4587,7 @@
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
     </row>
-    <row r="131" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4670,7 +4615,7 @@
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
     </row>
-    <row r="132" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4698,7 +4643,7 @@
       <c r="Y132" s="1"/>
       <c r="Z132" s="1"/>
     </row>
-    <row r="133" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4726,7 +4671,7 @@
       <c r="Y133" s="1"/>
       <c r="Z133" s="1"/>
     </row>
-    <row r="134" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4754,7 +4699,7 @@
       <c r="Y134" s="1"/>
       <c r="Z134" s="1"/>
     </row>
-    <row r="135" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4782,7 +4727,7 @@
       <c r="Y135" s="1"/>
       <c r="Z135" s="1"/>
     </row>
-    <row r="136" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4810,7 +4755,7 @@
       <c r="Y136" s="1"/>
       <c r="Z136" s="1"/>
     </row>
-    <row r="137" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4838,7 +4783,7 @@
       <c r="Y137" s="1"/>
       <c r="Z137" s="1"/>
     </row>
-    <row r="138" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4866,7 +4811,7 @@
       <c r="Y138" s="1"/>
       <c r="Z138" s="1"/>
     </row>
-    <row r="139" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4894,7 +4839,7 @@
       <c r="Y139" s="1"/>
       <c r="Z139" s="1"/>
     </row>
-    <row r="140" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4922,7 +4867,7 @@
       <c r="Y140" s="1"/>
       <c r="Z140" s="1"/>
     </row>
-    <row r="141" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -4950,7 +4895,7 @@
       <c r="Y141" s="1"/>
       <c r="Z141" s="1"/>
     </row>
-    <row r="142" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -4978,7 +4923,7 @@
       <c r="Y142" s="1"/>
       <c r="Z142" s="1"/>
     </row>
-    <row r="143" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5006,7 +4951,7 @@
       <c r="Y143" s="1"/>
       <c r="Z143" s="1"/>
     </row>
-    <row r="144" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5034,7 +4979,7 @@
       <c r="Y144" s="1"/>
       <c r="Z144" s="1"/>
     </row>
-    <row r="145" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -5062,7 +5007,7 @@
       <c r="Y145" s="1"/>
       <c r="Z145" s="1"/>
     </row>
-    <row r="146" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -5090,7 +5035,7 @@
       <c r="Y146" s="1"/>
       <c r="Z146" s="1"/>
     </row>
-    <row r="147" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -5118,7 +5063,7 @@
       <c r="Y147" s="1"/>
       <c r="Z147" s="1"/>
     </row>
-    <row r="148" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -5146,7 +5091,7 @@
       <c r="Y148" s="1"/>
       <c r="Z148" s="1"/>
     </row>
-    <row r="149" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -5174,7 +5119,7 @@
       <c r="Y149" s="1"/>
       <c r="Z149" s="1"/>
     </row>
-    <row r="150" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5202,7 +5147,7 @@
       <c r="Y150" s="1"/>
       <c r="Z150" s="1"/>
     </row>
-    <row r="151" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5230,7 +5175,7 @@
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
     </row>
-    <row r="152" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -5258,7 +5203,7 @@
       <c r="Y152" s="1"/>
       <c r="Z152" s="1"/>
     </row>
-    <row r="153" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -5286,7 +5231,7 @@
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
     </row>
-    <row r="154" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5314,7 +5259,7 @@
       <c r="Y154" s="1"/>
       <c r="Z154" s="1"/>
     </row>
-    <row r="155" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -5342,7 +5287,7 @@
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
     </row>
-    <row r="156" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5370,7 +5315,7 @@
       <c r="Y156" s="1"/>
       <c r="Z156" s="1"/>
     </row>
-    <row r="157" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -5398,7 +5343,7 @@
       <c r="Y157" s="1"/>
       <c r="Z157" s="1"/>
     </row>
-    <row r="158" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -5426,7 +5371,7 @@
       <c r="Y158" s="1"/>
       <c r="Z158" s="1"/>
     </row>
-    <row r="159" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -5454,7 +5399,7 @@
       <c r="Y159" s="1"/>
       <c r="Z159" s="1"/>
     </row>
-    <row r="160" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -5482,7 +5427,7 @@
       <c r="Y160" s="1"/>
       <c r="Z160" s="1"/>
     </row>
-    <row r="161" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -5510,7 +5455,7 @@
       <c r="Y161" s="1"/>
       <c r="Z161" s="1"/>
     </row>
-    <row r="162" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5538,7 +5483,7 @@
       <c r="Y162" s="1"/>
       <c r="Z162" s="1"/>
     </row>
-    <row r="163" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -5566,7 +5511,7 @@
       <c r="Y163" s="1"/>
       <c r="Z163" s="1"/>
     </row>
-    <row r="164" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5594,7 +5539,7 @@
       <c r="Y164" s="1"/>
       <c r="Z164" s="1"/>
     </row>
-    <row r="165" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5622,7 +5567,7 @@
       <c r="Y165" s="1"/>
       <c r="Z165" s="1"/>
     </row>
-    <row r="166" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5650,7 +5595,7 @@
       <c r="Y166" s="1"/>
       <c r="Z166" s="1"/>
     </row>
-    <row r="167" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5678,7 +5623,7 @@
       <c r="Y167" s="1"/>
       <c r="Z167" s="1"/>
     </row>
-    <row r="168" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5706,7 +5651,7 @@
       <c r="Y168" s="1"/>
       <c r="Z168" s="1"/>
     </row>
-    <row r="169" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5735,57 +5680,50 @@
       <c r="Z169" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="48">
+    <mergeCell ref="A82:I82"/>
+    <mergeCell ref="A83:I83"/>
     <mergeCell ref="A84:I84"/>
+    <mergeCell ref="B77:G77"/>
+    <mergeCell ref="B78:G78"/>
+    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="A80:I80"/>
+    <mergeCell ref="A81:I81"/>
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
     <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B63:I63"/>
-    <mergeCell ref="B64:I64"/>
-    <mergeCell ref="B65:I65"/>
-    <mergeCell ref="B66:I66"/>
+    <mergeCell ref="B76:G76"/>
     <mergeCell ref="B67:I67"/>
     <mergeCell ref="A68:I68"/>
     <mergeCell ref="B69:G69"/>
     <mergeCell ref="B70:G70"/>
     <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="A82:I82"/>
-    <mergeCell ref="A83:I83"/>
-    <mergeCell ref="A1:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="D6:I6"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="G19:I38"/>
-    <mergeCell ref="B78:G78"/>
-    <mergeCell ref="A79:I79"/>
-    <mergeCell ref="A80:I80"/>
-    <mergeCell ref="A81:I81"/>
-    <mergeCell ref="D50:F59"/>
-    <mergeCell ref="G39:I39"/>
     <mergeCell ref="A62:I62"/>
-    <mergeCell ref="A40:C59"/>
+    <mergeCell ref="B63:I63"/>
+    <mergeCell ref="B64:I64"/>
+    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="B66:I66"/>
     <mergeCell ref="A60:C60"/>
     <mergeCell ref="D60:F60"/>
     <mergeCell ref="G60:I60"/>
-    <mergeCell ref="G40:I59"/>
-    <mergeCell ref="A3:B11"/>
-    <mergeCell ref="A19:C38"/>
+    <mergeCell ref="A18:I18"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F49"/>
-    <mergeCell ref="D19:F38"/>
+    <mergeCell ref="G39:I39"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A13:B17"/>
     <mergeCell ref="C13:I13"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:I17"/>
     <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:I17"/>
+    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="A3:B11"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="D6:I6"/>
     <mergeCell ref="D7:I7"/>
     <mergeCell ref="D8:I8"/>
     <mergeCell ref="D9:I9"/>
@@ -5795,5 +5733,6 @@
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="14" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/informes-templates/INFORME DE PC.xlsx
+++ b/public/informes-templates/INFORME DE PC.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1737323A-14A1-4D31-B526-62B41CFB2DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F01AE3B-5451-4782-A8CA-7DD43374D044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,39 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
-  <si>
-    <t>INFORME DE SERVICIO</t>
-  </si>
-  <si>
-    <t>EMPRESA / CLIENTE</t>
-  </si>
-  <si>
-    <t>CONTACTO</t>
-  </si>
-  <si>
-    <t>ORDEN DE COMPRA</t>
-  </si>
-  <si>
-    <t>COT</t>
-  </si>
-  <si>
-    <t>LINEA / AREA</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t xml:space="preserve">DESCRIPCION </t>
   </si>
   <si>
-    <t>TIPO</t>
-  </si>
-  <si>
     <t>CANTIDAD</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EQUIPO 1 </t>
   </si>
   <si>
     <t>DATOS DEL EQUIPO</t>
@@ -156,7 +129,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,28 +143,25 @@
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="8"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -199,19 +169,7 @@
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -219,11 +177,13 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -231,6 +191,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -238,9 +199,10 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -263,6 +225,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -436,15 +404,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -454,6 +419,90 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -474,26 +523,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -501,68 +538,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -579,55 +580,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -831,24 +783,24 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z169"/>
+  <dimension ref="A1:Z168"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="9" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -868,15 +820,15 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="12"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="39"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -896,17 +848,15 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="9"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="53"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -926,17 +876,15 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="9"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -956,17 +904,17 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="3" t="s">
-        <v>3</v>
+      <c r="A5" s="26" t="s">
+        <v>2</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="9"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="28"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -985,18 +933,28 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="3" t="s">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="9"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="41"/>
+      <c r="G6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1016,17 +974,15 @@
       <c r="Z6" s="1"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="9"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -1046,17 +1002,19 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="3" t="s">
-        <v>6</v>
+      <c r="A8" s="2" t="s">
+        <v>9</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="9"/>
+      <c r="B8" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1076,17 +1034,15 @@
       <c r="Z8" s="1"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="9"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="33"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -1106,17 +1062,17 @@
       <c r="Z9" s="1"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="3" t="s">
-        <v>8</v>
+      <c r="A10" s="45" t="s">
+        <v>11</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="9"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="41"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -1136,17 +1092,15 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="8"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="7"/>
       <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="9"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="8"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -1166,14 +1120,14 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
-      <c r="B12" s="11"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="10"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="10"/>
       <c r="I12" s="11"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1194,19 +1148,15 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="22"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="11"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -1226,27 +1176,15 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="22"/>
-      <c r="G14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="A14" s="9"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="11"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -1266,15 +1204,15 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="11"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -1294,19 +1232,15 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="24"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="9"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="11"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -1326,15 +1260,15 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="26"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="9"/>
       <c r="E17" s="10"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="12"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="11"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -1354,17 +1288,15 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="22"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="11"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -1384,15 +1316,15 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="36"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="11"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -1412,15 +1344,15 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="37"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="39"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="11"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -1440,15 +1372,15 @@
       <c r="Z20" s="1"/>
     </row>
     <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="37"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="39"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="11"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -1468,15 +1400,15 @@
       <c r="Z21" s="1"/>
     </row>
     <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="37"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="39"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="11"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -1496,15 +1428,15 @@
       <c r="Z22" s="1"/>
     </row>
     <row r="23" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="37"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="39"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="11"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -1524,15 +1456,15 @@
       <c r="Z23" s="1"/>
     </row>
     <row r="24" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="37"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="39"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="11"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -1552,15 +1484,15 @@
       <c r="Z24" s="1"/>
     </row>
     <row r="25" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="37"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="39"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="11"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -1580,15 +1512,15 @@
       <c r="Z25" s="1"/>
     </row>
     <row r="26" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="37"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="39"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="11"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -1608,15 +1540,15 @@
       <c r="Z26" s="1"/>
     </row>
     <row r="27" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="37"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="39"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="11"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -1636,15 +1568,15 @@
       <c r="Z27" s="1"/>
     </row>
     <row r="28" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="37"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="39"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="11"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -1664,15 +1596,15 @@
       <c r="Z28" s="1"/>
     </row>
     <row r="29" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="37"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="39"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="11"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -1692,15 +1624,15 @@
       <c r="Z29" s="1"/>
     </row>
     <row r="30" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="37"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="39"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="14"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -1719,16 +1651,22 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="37"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="39"/>
+    <row r="31" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="44"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="44"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="44"/>
+      <c r="I31" s="41"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -1747,16 +1685,16 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="37"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="39"/>
+    <row r="32" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="8"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -1775,16 +1713,16 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="37"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="39"/>
+    <row r="33" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="9"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="11"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -1803,16 +1741,16 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="37"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="39"/>
+    <row r="34" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="9"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="11"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -1831,16 +1769,16 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="37"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="38"/>
-      <c r="I35" s="39"/>
+    <row r="35" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="9"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="11"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -1859,16 +1797,16 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="37"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="37"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="39"/>
+    <row r="36" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="9"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="11"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -1887,16 +1825,16 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="37"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="39"/>
+    <row r="37" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="9"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="11"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -1915,16 +1853,16 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="37"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="41"/>
-      <c r="I38" s="42"/>
+    <row r="38" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="9"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="11"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -1944,21 +1882,15 @@
       <c r="Z38" s="1"/>
     </row>
     <row r="39" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" s="21"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E39" s="21"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H39" s="21"/>
-      <c r="I39" s="22"/>
+      <c r="A39" s="9"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="11"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -1978,15 +1910,15 @@
       <c r="Z39" s="1"/>
     </row>
     <row r="40" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="34"/>
-      <c r="B40" s="35"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="36"/>
+      <c r="A40" s="9"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="11"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -2006,15 +1938,15 @@
       <c r="Z40" s="1"/>
     </row>
     <row r="41" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="37"/>
-      <c r="B41" s="38"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="38"/>
-      <c r="I41" s="39"/>
+      <c r="A41" s="9"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="11"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -2034,15 +1966,15 @@
       <c r="Z41" s="1"/>
     </row>
     <row r="42" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="37"/>
-      <c r="B42" s="38"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="38"/>
-      <c r="F42" s="39"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="38"/>
-      <c r="I42" s="39"/>
+      <c r="A42" s="9"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="11"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -2062,15 +1994,15 @@
       <c r="Z42" s="1"/>
     </row>
     <row r="43" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="37"/>
-      <c r="B43" s="38"/>
-      <c r="C43" s="39"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="37"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="39"/>
+      <c r="A43" s="9"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="11"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -2090,15 +2022,15 @@
       <c r="Z43" s="1"/>
     </row>
     <row r="44" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="37"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="39"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="37"/>
-      <c r="H44" s="38"/>
-      <c r="I44" s="39"/>
+      <c r="A44" s="9"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="11"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
@@ -2118,15 +2050,15 @@
       <c r="Z44" s="1"/>
     </row>
     <row r="45" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="37"/>
-      <c r="B45" s="38"/>
-      <c r="C45" s="39"/>
-      <c r="D45" s="37"/>
-      <c r="E45" s="38"/>
-      <c r="F45" s="39"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="38"/>
-      <c r="I45" s="39"/>
+      <c r="A45" s="9"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="11"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
@@ -2146,15 +2078,15 @@
       <c r="Z45" s="1"/>
     </row>
     <row r="46" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="37"/>
-      <c r="B46" s="38"/>
-      <c r="C46" s="39"/>
-      <c r="D46" s="37"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="39"/>
-      <c r="G46" s="37"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="39"/>
+      <c r="A46" s="9"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="11"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
@@ -2174,15 +2106,15 @@
       <c r="Z46" s="1"/>
     </row>
     <row r="47" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="37"/>
-      <c r="B47" s="38"/>
-      <c r="C47" s="39"/>
-      <c r="D47" s="37"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="39"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="38"/>
-      <c r="I47" s="39"/>
+      <c r="A47" s="9"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="11"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -2202,15 +2134,15 @@
       <c r="Z47" s="1"/>
     </row>
     <row r="48" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="37"/>
-      <c r="B48" s="38"/>
-      <c r="C48" s="39"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="38"/>
-      <c r="F48" s="39"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="38"/>
-      <c r="I48" s="39"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="11"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -2230,15 +2162,15 @@
       <c r="Z48" s="1"/>
     </row>
     <row r="49" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="37"/>
-      <c r="B49" s="38"/>
-      <c r="C49" s="39"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="42"/>
-      <c r="G49" s="37"/>
-      <c r="H49" s="38"/>
-      <c r="I49" s="39"/>
+      <c r="A49" s="9"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="11"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -2258,15 +2190,15 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="37"/>
-      <c r="B50" s="38"/>
-      <c r="C50" s="39"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="35"/>
-      <c r="F50" s="36"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="38"/>
-      <c r="I50" s="39"/>
+      <c r="A50" s="9"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="11"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -2286,15 +2218,15 @@
       <c r="Z50" s="1"/>
     </row>
     <row r="51" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="37"/>
-      <c r="B51" s="38"/>
-      <c r="C51" s="39"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="38"/>
-      <c r="F51" s="39"/>
-      <c r="G51" s="37"/>
-      <c r="H51" s="38"/>
-      <c r="I51" s="39"/>
+      <c r="A51" s="9"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="14"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -2314,15 +2246,21 @@
       <c r="Z51" s="1"/>
     </row>
     <row r="52" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="37"/>
-      <c r="B52" s="38"/>
-      <c r="C52" s="39"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="39"/>
-      <c r="G52" s="37"/>
-      <c r="H52" s="38"/>
-      <c r="I52" s="39"/>
+      <c r="A52" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" s="44"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="44"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="H52" s="44"/>
+      <c r="I52" s="41"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -2342,15 +2280,15 @@
       <c r="Z52" s="1"/>
     </row>
     <row r="53" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="37"/>
-      <c r="B53" s="38"/>
-      <c r="C53" s="39"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="38"/>
-      <c r="F53" s="39"/>
-      <c r="G53" s="37"/>
-      <c r="H53" s="38"/>
-      <c r="I53" s="39"/>
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -2370,15 +2308,17 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="54" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="37"/>
-      <c r="B54" s="38"/>
-      <c r="C54" s="39"/>
-      <c r="D54" s="37"/>
-      <c r="E54" s="38"/>
-      <c r="F54" s="39"/>
-      <c r="G54" s="37"/>
-      <c r="H54" s="38"/>
-      <c r="I54" s="39"/>
+      <c r="A54" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54" s="44"/>
+      <c r="C54" s="44"/>
+      <c r="D54" s="44"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="44"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="41"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -2398,15 +2338,19 @@
       <c r="Z54" s="1"/>
     </row>
     <row r="55" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="37"/>
-      <c r="B55" s="38"/>
-      <c r="C55" s="39"/>
-      <c r="D55" s="37"/>
-      <c r="E55" s="38"/>
-      <c r="F55" s="39"/>
-      <c r="G55" s="37"/>
-      <c r="H55" s="38"/>
-      <c r="I55" s="39"/>
+      <c r="A55" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B55" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" s="44"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="44"/>
+      <c r="G55" s="44"/>
+      <c r="H55" s="44"/>
+      <c r="I55" s="41"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -2426,15 +2370,15 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="37"/>
-      <c r="B56" s="38"/>
-      <c r="C56" s="39"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="38"/>
-      <c r="F56" s="39"/>
-      <c r="G56" s="37"/>
-      <c r="H56" s="38"/>
-      <c r="I56" s="39"/>
+      <c r="A56" s="3"/>
+      <c r="B56" s="42"/>
+      <c r="C56" s="44"/>
+      <c r="D56" s="44"/>
+      <c r="E56" s="44"/>
+      <c r="F56" s="44"/>
+      <c r="G56" s="44"/>
+      <c r="H56" s="44"/>
+      <c r="I56" s="41"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
@@ -2454,15 +2398,15 @@
       <c r="Z56" s="1"/>
     </row>
     <row r="57" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="37"/>
-      <c r="B57" s="38"/>
-      <c r="C57" s="39"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="38"/>
-      <c r="F57" s="39"/>
-      <c r="G57" s="37"/>
-      <c r="H57" s="38"/>
-      <c r="I57" s="39"/>
+      <c r="A57" s="3"/>
+      <c r="B57" s="42"/>
+      <c r="C57" s="44"/>
+      <c r="D57" s="44"/>
+      <c r="E57" s="44"/>
+      <c r="F57" s="44"/>
+      <c r="G57" s="44"/>
+      <c r="H57" s="44"/>
+      <c r="I57" s="41"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
@@ -2482,15 +2426,15 @@
       <c r="Z57" s="1"/>
     </row>
     <row r="58" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="37"/>
-      <c r="B58" s="38"/>
-      <c r="C58" s="39"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="38"/>
-      <c r="F58" s="39"/>
-      <c r="G58" s="37"/>
-      <c r="H58" s="38"/>
-      <c r="I58" s="39"/>
+      <c r="A58" s="3"/>
+      <c r="B58" s="42"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="44"/>
+      <c r="F58" s="44"/>
+      <c r="G58" s="44"/>
+      <c r="H58" s="44"/>
+      <c r="I58" s="41"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
@@ -2510,15 +2454,15 @@
       <c r="Z58" s="1"/>
     </row>
     <row r="59" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="37"/>
-      <c r="B59" s="38"/>
-      <c r="C59" s="39"/>
-      <c r="D59" s="40"/>
-      <c r="E59" s="41"/>
-      <c r="F59" s="42"/>
-      <c r="G59" s="40"/>
-      <c r="H59" s="41"/>
-      <c r="I59" s="42"/>
+      <c r="A59" s="3"/>
+      <c r="B59" s="42"/>
+      <c r="C59" s="44"/>
+      <c r="D59" s="44"/>
+      <c r="E59" s="44"/>
+      <c r="F59" s="44"/>
+      <c r="G59" s="44"/>
+      <c r="H59" s="44"/>
+      <c r="I59" s="41"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -2538,21 +2482,15 @@
       <c r="Z59" s="1"/>
     </row>
     <row r="60" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B60" s="21"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="E60" s="21"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="H60" s="21"/>
-      <c r="I60" s="22"/>
+      <c r="A60" s="3"/>
+      <c r="B60" s="42"/>
+      <c r="C60" s="44"/>
+      <c r="D60" s="44"/>
+      <c r="E60" s="44"/>
+      <c r="F60" s="44"/>
+      <c r="G60" s="44"/>
+      <c r="H60" s="44"/>
+      <c r="I60" s="41"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
@@ -2572,15 +2510,17 @@
       <c r="Z60" s="1"/>
     </row>
     <row r="61" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="5"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="5"/>
+      <c r="A61" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="B61" s="35"/>
+      <c r="C61" s="35"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="35"/>
+      <c r="F61" s="35"/>
+      <c r="G61" s="35"/>
+      <c r="H61" s="35"/>
+      <c r="I61" s="36"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
@@ -2600,17 +2540,23 @@
       <c r="Z61" s="1"/>
     </row>
     <row r="62" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="28" t="s">
-        <v>27</v>
+      <c r="A62" s="2" t="s">
+        <v>21</v>
       </c>
-      <c r="B62" s="21"/>
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="21"/>
-      <c r="G62" s="21"/>
-      <c r="H62" s="21"/>
-      <c r="I62" s="22"/>
+      <c r="B62" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" s="44"/>
+      <c r="D62" s="44"/>
+      <c r="E62" s="44"/>
+      <c r="F62" s="44"/>
+      <c r="G62" s="44"/>
+      <c r="H62" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
@@ -2630,19 +2576,19 @@
       <c r="Z62" s="1"/>
     </row>
     <row r="63" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>8</v>
+      <c r="A63" s="5">
+        <v>1</v>
       </c>
-      <c r="B63" s="20" t="s">
-        <v>28</v>
+      <c r="B63" s="47" t="s">
+        <v>25</v>
       </c>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
-      <c r="H63" s="21"/>
-      <c r="I63" s="22"/>
+      <c r="C63" s="44"/>
+      <c r="D63" s="44"/>
+      <c r="E63" s="44"/>
+      <c r="F63" s="44"/>
+      <c r="G63" s="41"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
@@ -2662,15 +2608,19 @@
       <c r="Z63" s="1"/>
     </row>
     <row r="64" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="4"/>
-      <c r="B64" s="23"/>
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
-      <c r="H64" s="21"/>
-      <c r="I64" s="22"/>
+      <c r="A64" s="5">
+        <v>2</v>
+      </c>
+      <c r="B64" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" s="44"/>
+      <c r="D64" s="44"/>
+      <c r="E64" s="44"/>
+      <c r="F64" s="44"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -2690,15 +2640,19 @@
       <c r="Z64" s="1"/>
     </row>
     <row r="65" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="4"/>
-      <c r="B65" s="23"/>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
-      <c r="H65" s="21"/>
-      <c r="I65" s="22"/>
+      <c r="A65" s="5">
+        <v>3</v>
+      </c>
+      <c r="B65" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65" s="44"/>
+      <c r="D65" s="44"/>
+      <c r="E65" s="44"/>
+      <c r="F65" s="44"/>
+      <c r="G65" s="41"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
@@ -2718,15 +2672,19 @@
       <c r="Z65" s="1"/>
     </row>
     <row r="66" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="4"/>
-      <c r="B66" s="23"/>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
-      <c r="H66" s="21"/>
-      <c r="I66" s="22"/>
+      <c r="A66" s="5">
+        <v>4</v>
+      </c>
+      <c r="B66" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="C66" s="44"/>
+      <c r="D66" s="44"/>
+      <c r="E66" s="44"/>
+      <c r="F66" s="44"/>
+      <c r="G66" s="41"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
@@ -2746,15 +2704,19 @@
       <c r="Z66" s="1"/>
     </row>
     <row r="67" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="4"/>
-      <c r="B67" s="23"/>
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
-      <c r="G67" s="21"/>
-      <c r="H67" s="21"/>
-      <c r="I67" s="22"/>
+      <c r="A67" s="5">
+        <v>5</v>
+      </c>
+      <c r="B67" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" s="44"/>
+      <c r="D67" s="44"/>
+      <c r="E67" s="44"/>
+      <c r="F67" s="44"/>
+      <c r="G67" s="41"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
@@ -2774,17 +2736,19 @@
       <c r="Z67" s="1"/>
     </row>
     <row r="68" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="29" t="s">
-        <v>29</v>
+      <c r="A68" s="5">
+        <v>6</v>
       </c>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="9"/>
+      <c r="B68" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="C68" s="44"/>
+      <c r="D68" s="44"/>
+      <c r="E68" s="44"/>
+      <c r="F68" s="44"/>
+      <c r="G68" s="41"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
@@ -2804,23 +2768,19 @@
       <c r="Z68" s="1"/>
     </row>
     <row r="69" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>30</v>
+      <c r="A69" s="5">
+        <v>7</v>
       </c>
-      <c r="B69" s="20" t="s">
+      <c r="B69" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="C69" s="44"/>
+      <c r="D69" s="44"/>
+      <c r="E69" s="44"/>
+      <c r="F69" s="44"/>
+      <c r="G69" s="41"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
@@ -2840,19 +2800,19 @@
       <c r="Z69" s="1"/>
     </row>
     <row r="70" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="6">
-        <v>1</v>
+      <c r="A70" s="5">
+        <v>8</v>
       </c>
-      <c r="B70" s="30" t="s">
-        <v>34</v>
+      <c r="B70" s="47" t="s">
+        <v>32</v>
       </c>
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="22"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
+      <c r="C70" s="44"/>
+      <c r="D70" s="44"/>
+      <c r="E70" s="44"/>
+      <c r="F70" s="44"/>
+      <c r="G70" s="41"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
@@ -2872,19 +2832,19 @@
       <c r="Z70" s="1"/>
     </row>
     <row r="71" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="6">
-        <v>2</v>
+      <c r="A71" s="5">
+        <v>9</v>
       </c>
-      <c r="B71" s="30" t="s">
-        <v>35</v>
+      <c r="B71" s="47" t="s">
+        <v>33</v>
       </c>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="22"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
+      <c r="C71" s="44"/>
+      <c r="D71" s="44"/>
+      <c r="E71" s="44"/>
+      <c r="F71" s="44"/>
+      <c r="G71" s="41"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
@@ -2904,19 +2864,17 @@
       <c r="Z71" s="1"/>
     </row>
     <row r="72" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="6">
-        <v>3</v>
+      <c r="A72" s="48" t="s">
+        <v>34</v>
       </c>
-      <c r="B72" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="22"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
+      <c r="B72" s="35"/>
+      <c r="C72" s="35"/>
+      <c r="D72" s="35"/>
+      <c r="E72" s="35"/>
+      <c r="F72" s="35"/>
+      <c r="G72" s="35"/>
+      <c r="H72" s="35"/>
+      <c r="I72" s="36"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
@@ -2936,19 +2894,15 @@
       <c r="Z72" s="1"/>
     </row>
     <row r="73" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="6">
-        <v>4</v>
-      </c>
-      <c r="B73" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="22"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
+      <c r="A73" s="50"/>
+      <c r="B73" s="35"/>
+      <c r="C73" s="35"/>
+      <c r="D73" s="35"/>
+      <c r="E73" s="35"/>
+      <c r="F73" s="35"/>
+      <c r="G73" s="35"/>
+      <c r="H73" s="35"/>
+      <c r="I73" s="36"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
@@ -2968,19 +2922,15 @@
       <c r="Z73" s="1"/>
     </row>
     <row r="74" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="6">
-        <v>5</v>
-      </c>
-      <c r="B74" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="22"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
+      <c r="A74" s="50"/>
+      <c r="B74" s="35"/>
+      <c r="C74" s="35"/>
+      <c r="D74" s="35"/>
+      <c r="E74" s="35"/>
+      <c r="F74" s="35"/>
+      <c r="G74" s="35"/>
+      <c r="H74" s="35"/>
+      <c r="I74" s="36"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
@@ -3000,19 +2950,15 @@
       <c r="Z74" s="1"/>
     </row>
     <row r="75" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="6">
-        <v>6</v>
-      </c>
-      <c r="B75" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="22"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
+      <c r="A75" s="50"/>
+      <c r="B75" s="35"/>
+      <c r="C75" s="35"/>
+      <c r="D75" s="35"/>
+      <c r="E75" s="35"/>
+      <c r="F75" s="35"/>
+      <c r="G75" s="35"/>
+      <c r="H75" s="35"/>
+      <c r="I75" s="36"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
@@ -3032,19 +2978,15 @@
       <c r="Z75" s="1"/>
     </row>
     <row r="76" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="6">
-        <v>7</v>
-      </c>
-      <c r="B76" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="22"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
+      <c r="A76" s="50"/>
+      <c r="B76" s="35"/>
+      <c r="C76" s="35"/>
+      <c r="D76" s="35"/>
+      <c r="E76" s="35"/>
+      <c r="F76" s="35"/>
+      <c r="G76" s="35"/>
+      <c r="H76" s="35"/>
+      <c r="I76" s="36"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
@@ -3064,19 +3006,15 @@
       <c r="Z76" s="1"/>
     </row>
     <row r="77" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="6">
-        <v>8</v>
-      </c>
-      <c r="B77" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="C77" s="21"/>
-      <c r="D77" s="21"/>
-      <c r="E77" s="21"/>
-      <c r="F77" s="21"/>
-      <c r="G77" s="22"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
+      <c r="A77" s="50"/>
+      <c r="B77" s="35"/>
+      <c r="C77" s="35"/>
+      <c r="D77" s="35"/>
+      <c r="E77" s="35"/>
+      <c r="F77" s="35"/>
+      <c r="G77" s="35"/>
+      <c r="H77" s="35"/>
+      <c r="I77" s="36"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
@@ -3096,19 +3034,17 @@
       <c r="Z77" s="1"/>
     </row>
     <row r="78" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="6">
-        <v>9</v>
+      <c r="A78" s="48" t="s">
+        <v>35</v>
       </c>
-      <c r="B78" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="C78" s="21"/>
-      <c r="D78" s="21"/>
-      <c r="E78" s="21"/>
-      <c r="F78" s="21"/>
-      <c r="G78" s="22"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
+      <c r="B78" s="35"/>
+      <c r="C78" s="35"/>
+      <c r="D78" s="35"/>
+      <c r="E78" s="35"/>
+      <c r="F78" s="35"/>
+      <c r="G78" s="35"/>
+      <c r="H78" s="35"/>
+      <c r="I78" s="36"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
@@ -3128,17 +3064,15 @@
       <c r="Z78" s="1"/>
     </row>
     <row r="79" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="9"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="44"/>
+      <c r="C79" s="44"/>
+      <c r="D79" s="44"/>
+      <c r="E79" s="44"/>
+      <c r="F79" s="44"/>
+      <c r="G79" s="44"/>
+      <c r="H79" s="44"/>
+      <c r="I79" s="41"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
@@ -3158,15 +3092,15 @@
       <c r="Z79" s="1"/>
     </row>
     <row r="80" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="32"/>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="8"/>
-      <c r="I80" s="9"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="44"/>
+      <c r="C80" s="44"/>
+      <c r="D80" s="44"/>
+      <c r="E80" s="44"/>
+      <c r="F80" s="44"/>
+      <c r="G80" s="44"/>
+      <c r="H80" s="44"/>
+      <c r="I80" s="41"/>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
@@ -3186,15 +3120,15 @@
       <c r="Z80" s="1"/>
     </row>
     <row r="81" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="32"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="9"/>
+      <c r="A81" s="49"/>
+      <c r="B81" s="44"/>
+      <c r="C81" s="44"/>
+      <c r="D81" s="44"/>
+      <c r="E81" s="44"/>
+      <c r="F81" s="44"/>
+      <c r="G81" s="44"/>
+      <c r="H81" s="44"/>
+      <c r="I81" s="41"/>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
@@ -3214,17 +3148,15 @@
       <c r="Z81" s="1"/>
     </row>
     <row r="82" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="9"/>
+      <c r="A82" s="49"/>
+      <c r="B82" s="44"/>
+      <c r="C82" s="44"/>
+      <c r="D82" s="44"/>
+      <c r="E82" s="44"/>
+      <c r="F82" s="44"/>
+      <c r="G82" s="44"/>
+      <c r="H82" s="44"/>
+      <c r="I82" s="41"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
@@ -3244,15 +3176,15 @@
       <c r="Z82" s="1"/>
     </row>
     <row r="83" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="33"/>
-      <c r="B83" s="21"/>
-      <c r="C83" s="21"/>
-      <c r="D83" s="21"/>
-      <c r="E83" s="21"/>
-      <c r="F83" s="21"/>
-      <c r="G83" s="21"/>
-      <c r="H83" s="21"/>
-      <c r="I83" s="22"/>
+      <c r="A83" s="49"/>
+      <c r="B83" s="44"/>
+      <c r="C83" s="44"/>
+      <c r="D83" s="44"/>
+      <c r="E83" s="44"/>
+      <c r="F83" s="44"/>
+      <c r="G83" s="44"/>
+      <c r="H83" s="44"/>
+      <c r="I83" s="41"/>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
@@ -3272,15 +3204,15 @@
       <c r="Z83" s="1"/>
     </row>
     <row r="84" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="33"/>
-      <c r="B84" s="21"/>
-      <c r="C84" s="21"/>
-      <c r="D84" s="21"/>
-      <c r="E84" s="21"/>
-      <c r="F84" s="21"/>
-      <c r="G84" s="21"/>
-      <c r="H84" s="21"/>
-      <c r="I84" s="22"/>
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
@@ -5651,88 +5583,60 @@
       <c r="Y168" s="1"/>
       <c r="Z168" s="1"/>
     </row>
-    <row r="169" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="1"/>
-      <c r="B169" s="1"/>
-      <c r="C169" s="1"/>
-      <c r="D169" s="1"/>
-      <c r="E169" s="1"/>
-      <c r="F169" s="1"/>
-      <c r="G169" s="1"/>
-      <c r="H169" s="1"/>
-      <c r="I169" s="1"/>
-      <c r="J169" s="1"/>
-      <c r="K169" s="1"/>
-      <c r="L169" s="1"/>
-      <c r="M169" s="1"/>
-      <c r="N169" s="1"/>
-      <c r="O169" s="1"/>
-      <c r="P169" s="1"/>
-      <c r="Q169" s="1"/>
-      <c r="R169" s="1"/>
-      <c r="S169" s="1"/>
-      <c r="T169" s="1"/>
-      <c r="U169" s="1"/>
-      <c r="V169" s="1"/>
-      <c r="W169" s="1"/>
-      <c r="X169" s="1"/>
-      <c r="Y169" s="1"/>
-      <c r="Z169" s="1"/>
-    </row>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="A82:I82"/>
+  <mergeCells count="49">
+    <mergeCell ref="A78:I78"/>
+    <mergeCell ref="A79:I79"/>
     <mergeCell ref="A83:I83"/>
-    <mergeCell ref="A84:I84"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="B78:G78"/>
-    <mergeCell ref="A79:I79"/>
-    <mergeCell ref="A80:I80"/>
-    <mergeCell ref="A81:I81"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B67:I67"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="B69:G69"/>
     <mergeCell ref="B70:G70"/>
     <mergeCell ref="B71:G71"/>
-    <mergeCell ref="A62:I62"/>
-    <mergeCell ref="B63:I63"/>
-    <mergeCell ref="B64:I64"/>
-    <mergeCell ref="B65:I65"/>
-    <mergeCell ref="B66:I66"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="G60:I60"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A13:B17"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:I17"/>
-    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="A72:I72"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A75:I75"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A82:I82"/>
+    <mergeCell ref="A81:I81"/>
+    <mergeCell ref="A80:I80"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B68:G68"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="A54:I54"/>
+    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="B59:I59"/>
+    <mergeCell ref="B58:I58"/>
     <mergeCell ref="A1:I2"/>
-    <mergeCell ref="A3:B11"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="D6:I6"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:I9"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="14" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>